--- a/Assignment 1 - Test cases.xlsx
+++ b/Assignment 1 - Test cases.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\test_automation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\test_1automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38167E21-0DF5-4C80-A50F-2E81A6C83849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5D5CE8C-962C-4CDC-B584-B7217FFD4C90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="722" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="280">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -494,13 +494,379 @@
   </si>
   <si>
     <t>@සමන් අයියේ ASAP file එක එවන්න!</t>
+  </si>
+  <si>
+    <t>Singlish input types covered</t>
+  </si>
+  <si>
+    <t>Evidence or rationale for the input type covered</t>
+  </si>
+  <si>
+    <t>Question forms</t>
+  </si>
+  <si>
+    <t>Command forms</t>
+  </si>
+  <si>
+    <t>Greetings</t>
+  </si>
+  <si>
+    <t>Requests</t>
+  </si>
+  <si>
+    <t>Responses</t>
+  </si>
+  <si>
+    <t>Repeated Words</t>
+  </si>
+  <si>
+    <t>Inputs with punctuation marks</t>
+  </si>
+  <si>
+    <t>Romanization / Spelling Variants</t>
+  </si>
+  <si>
+    <t>Isolated English Word Insertions in Singlish</t>
+  </si>
+  <si>
+    <t>Multi-Word English Phrases in Singlish</t>
+  </si>
+  <si>
+    <t>English Digital Terms in Singlish</t>
+  </si>
+  <si>
+    <t>Platform/App Names in Singlish</t>
+  </si>
+  <si>
+    <t>English Abbreviations/Acronyms in Singlish</t>
+  </si>
+  <si>
+    <t>English Clipped Forms in Singlish</t>
+  </si>
+  <si>
+    <t>Place Names Embedded in Singlish</t>
+  </si>
+  <si>
+    <t>Person Names Embedded in Singlish</t>
+  </si>
+  <si>
+    <t>Inputs with Numbers and Numeric Suffixes</t>
+  </si>
+  <si>
+    <t>Inputs with Currency</t>
+  </si>
+  <si>
+    <t>Inputs with Time Formats</t>
+  </si>
+  <si>
+    <t>Inputs with Dates</t>
+  </si>
+  <si>
+    <t>Inputs with Unit of Measurements</t>
+  </si>
+  <si>
+    <t>Inputs with Slang and Casual Phrasing</t>
+  </si>
+  <si>
+    <t>Online Identifiers in Singlish</t>
+  </si>
+  <si>
+    <t>Inputs Containing Emojis</t>
+  </si>
+  <si>
+    <t>Inputs with Currency, Inputs Containing Emojis</t>
+  </si>
+  <si>
+    <t>Online Identifiers in Singlish, English Abbreviations/Acronyms in Singlish</t>
+  </si>
+  <si>
+    <t>Rationale: The entire input is a question asking where the person is going tomorrow.</t>
+  </si>
+  <si>
+    <t>Rationale: The input is a question asking who came with the person today.</t>
+  </si>
+  <si>
+    <t>Rationale: The input is a direct command asking someone to show something.</t>
+  </si>
+  <si>
+    <t>Rationale: The input is a command instructing someone to call back later.</t>
+  </si>
+  <si>
+    <t>Rationale: The input is a greeting wishing someone a good day.</t>
+  </si>
+  <si>
+    <t>Rationale: The input is an informal greeting asking how someone is doing.</t>
+  </si>
+  <si>
+    <t>Rationale: The input is a polite request to send a file.</t>
+  </si>
+  <si>
+    <t>Rationale: The input is a polite request asking someone to wait and help.</t>
+  </si>
+  <si>
+    <t>Rationale: The input is a response declining and stating an alternative plan.</t>
+  </si>
+  <si>
+    <t>Rationale: The input is a casual acknowledgment response.</t>
+  </si>
+  <si>
+    <t>Rationale: 'hodai' is repeated twice for emphasis before a statement.</t>
+  </si>
+  <si>
+    <t>Rationale: 'nehe' is repeated twice for strong emphasis of refusal.</t>
+  </si>
+  <si>
+    <t>Rationale: Input uses ellipsis (...) and question mark (?) as punctuation.</t>
+  </si>
+  <si>
+    <t>Rationale: Input uses exclamation mark (!) and question mark (?) as punctuation.</t>
+  </si>
+  <si>
+    <t>Rationale: 'colombo' is spelled as 'columbo' and 'yanawa' as 'yanwa' — alternate romanizations.</t>
+  </si>
+  <si>
+    <t>Rationale: 'enna' is spelled as 'eenna' and 'one' as 'onee' — spelling variants used.</t>
+  </si>
+  <si>
+    <t>Rationale: Single English words 'project' and 'finish' are inserted in Singlish text.</t>
+  </si>
+  <si>
+    <t>Rationale: Single English words 'meeting' and 'late' are inserted in Singlish text.</t>
+  </si>
+  <si>
+    <t>Rationale: Multi-word English phrase 'out of office' is inserted inside Singlish input.</t>
+  </si>
+  <si>
+    <t>Rationale: Multi-word English phrase 'no worries, I will handle it' is inside Singlish text.</t>
+  </si>
+  <si>
+    <t>Rationale: Digital term 'screenshot' is inserted in Singlish text.</t>
+  </si>
+  <si>
+    <t>Rationale: Digital term 'bluetooth' is used inside a Singlish sentence.</t>
+  </si>
+  <si>
+    <t>Rationale: Platform name 'Facebook' is embedded inside Singlish text.</t>
+  </si>
+  <si>
+    <t>Rationale: App name 'Instagram' is embedded inside a Singlish question.</t>
+  </si>
+  <si>
+    <t>Rationale: Acronym 'ASAP' is used inside Singlish text.</t>
+  </si>
+  <si>
+    <t>Rationale: Technical acronym 'API' is embedded in Singlish input.</t>
+  </si>
+  <si>
+    <t>Rationale: Clipped English word 'doc' (short for document) is used in Singlish text.</t>
+  </si>
+  <si>
+    <t>Rationale: Clipped word 'uni' (short for university) is used in Singlish text.</t>
+  </si>
+  <si>
+    <t>Rationale: Place name 'Kandy' is embedded inside Singlish text.</t>
+  </si>
+  <si>
+    <t>Rationale: Place name 'Galle Face' is embedded inside Singlish text.</t>
+  </si>
+  <si>
+    <t>Rationale: Person name 'Kasun' is embedded inside Singlish text.</t>
+  </si>
+  <si>
+    <t>Rationale: Person names 'Nimasha' and 'Dilshan' are both embedded in Singlish text.</t>
+  </si>
+  <si>
+    <t>Rationale: Numeric suffix '3rd' is used inside a Singlish sentence.</t>
+  </si>
+  <si>
+    <t>Rationale: Number with suffix '25k' is used inside Singlish text.</t>
+  </si>
+  <si>
+    <t>Rationale: Currency 'Rs. 3500' is embedded inside Singlish text.</t>
+  </si>
+  <si>
+    <t>Rationale: Currency 'USD 150' is used inside a Singlish question.</t>
+  </si>
+  <si>
+    <t>Rationale: Time format '8:00AM' is embedded inside Singlish text.</t>
+  </si>
+  <si>
+    <t>Rationale: Time format '6.30pm' is embedded inside Singlish text.</t>
+  </si>
+  <si>
+    <t>Rationale: Date format '2026-03-15' is embedded inside Singlish text.</t>
+  </si>
+  <si>
+    <t>Rationale: Date 'March 20' in English format is embedded inside Singlish text.</t>
+  </si>
+  <si>
+    <t>Rationale: Unit of measurement 'kg 5k' is embedded inside Singlish text.</t>
+  </si>
+  <si>
+    <t>Rationale: Unit of measurement 'feet 12k' is embedded inside Singlish text.</t>
+  </si>
+  <si>
+    <t>Rationale: Slang words 'bro', 'uba', 'mara set' represent casual/slang phrasing.</t>
+  </si>
+  <si>
+    <t>Rationale: Casual expression 'aiyo' and informal phrasing used throughout.</t>
+  </si>
+  <si>
+    <t>Rationale: URL 'www.google.com' is embedded inside Singlish text.</t>
+  </si>
+  <si>
+    <t>Rationale: Online identifier '@Kamal' (mention tag) is embedded inside Singlish text.</t>
+  </si>
+  <si>
+    <t>Rationale: Emoji 😴 is embedded inside Singlish text.</t>
+  </si>
+  <si>
+    <t>Rationale: Emoji 😢 is embedded inside a Singlish sentence.</t>
+  </si>
+  <si>
+    <t>Rationale: Currency 'Rs. 500' and emoji 😄 are both embedded inside Singlish text.</t>
+  </si>
+  <si>
+    <t>Rationale: Online mention '@Saman' and acronym 'ASAP' are both embedded in Singlish text.</t>
+  </si>
+  <si>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t>කොහෙද ඔයා හෙට යන්නේ?</t>
+  </si>
+  <si>
+    <t>ඔයා අද කවුරු එක්ක ආවෙ?</t>
+  </si>
+  <si>
+    <t>එක දාල පෙන්නන්න මට.</t>
+  </si>
+  <si>
+    <t>නැවත phone කරන්නකො.</t>
+  </si>
+  <si>
+    <t>කොහොමද මචන්, හොඳට ඉන්නවද?</t>
+  </si>
+  <si>
+    <t>කරුණාකර file එක මට එවන්නකො.</t>
+  </si>
+  <si>
+    <t>පොඩ්ඩක් ඉදලා මට help කරන්න පුලුවන්ද?</t>
+  </si>
+  <si>
+    <t>නෑ, මම හෙට එන්න.</t>
+  </si>
+  <si>
+    <t>ok ok මම බලන්න.</t>
+  </si>
+  <si>
+    <t>හොඳයි හොඳයි මම ඔයාල එක්ක එන්න.</t>
+  </si>
+  <si>
+    <t>එන්නේ නෑ මම busy.</t>
+  </si>
+  <si>
+    <t>මට ඕනේ... එක දෙන්න පුලුවන්ද?</t>
+  </si>
+  <si>
+    <t>අපි යනවා ඔයා එනවද?</t>
+  </si>
+  <si>
+    <t>මම හෙට කොලඹ යනවා.</t>
+  </si>
+  <si>
+    <t>එයා ඇවිත් කිව්වා එන්න ඕන කියලා.</t>
+  </si>
+  <si>
+    <t>මම අද project එක finish කරා.</t>
+  </si>
+  <si>
+    <t>අපි හෙට meeting එකට late වෙනවා.</t>
+  </si>
+  <si>
+    <t>මම ඔයාල එක්ක out of office ඉන්නවා හෙට.</t>
+  </si>
+  <si>
+    <t>එයා කිව්වා no worries I will handle it කියලා.</t>
+  </si>
+  <si>
+    <t>මට ඔයා screenshot එක එවන්නකො.</t>
+  </si>
+  <si>
+    <t>bluetooth එක on කරන්න බෑ.</t>
+  </si>
+  <si>
+    <t>Facebook එකේ එයා post එක දැම්මා.</t>
+  </si>
+  <si>
+    <t>API එක work වෙන්නේ නෑ අපිට.</t>
+  </si>
+  <si>
+    <t>මම doc එක edit කරනවා.</t>
+  </si>
+  <si>
+    <t>හෙට uni එකේ presentation එක තියෙනවා.</t>
+  </si>
+  <si>
+    <t>අපි කන්ද වලට යන්න plan කරනවා.</t>
+  </si>
+  <si>
+    <t>කසුන් කිව්වා මම එනවා කියලා.</t>
+  </si>
+  <si>
+    <t>නිමාශා සහ දිල්ශාන් දෙන්න late ආවා.</t>
+  </si>
+  <si>
+    <t>class එකේ ළමයි 25ක් වගේ ඉන්නවා.</t>
+  </si>
+  <si>
+    <t>ඒ jacket එක Rs 3500ට ගත්තා.</t>
+  </si>
+  <si>
+    <t>අපි 6.30pm වලට meet වෙනවා.</t>
+  </si>
+  <si>
+    <t>interview එක 2026-03-15ට fix කරලා.</t>
+  </si>
+  <si>
+    <t>March 20 වෙනකන් assignment එක දෙන්න ඕන.</t>
+  </si>
+  <si>
+    <t>ඒ bag එක kg 5ක් වගේ තියෙනවා.</t>
+  </si>
+  <si>
+    <t>room එක feet 12ක් වගේ.</t>
+  </si>
+  <si>
+    <t>bro උඹ මේක කරලා දුන්නොත් මාර set.</t>
+  </si>
+  <si>
+    <t>අයියෝ එක නෑ කිව්වොත් මම පිස්සු වෙනවා.</t>
+  </si>
+  <si>
+    <t>@Kamal අයියේ ඔයා group එකට add උනාද?</t>
+  </si>
+  <si>
+    <t>මම ගොඩක් tired අපි හෙට යනවා 😴</t>
+  </si>
+  <si>
+    <t>එයා නෑ කිව්වා මට ලියෝ ගොඩක් 😢</t>
+  </si>
+  <si>
+    <t>මම අද Rs 500 දාල lunch ගත්තා 😄</t>
+  </si>
+  <si>
+    <t>@සමන් අයියේ ASAP file එක එවන්න</t>
+  </si>
+  <si>
+    <t>මට මේ ලින්ක් එක එවන්න www.google.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -521,16 +887,50 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF3FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF3FB"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -553,11 +953,40 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -574,8 +1003,25 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -854,7 +1300,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr defaultRowHeight="49.95" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.88671875" customWidth="1"/>
@@ -862,12 +1308,13 @@
     <col min="3" max="3" width="39.21875" customWidth="1"/>
     <col min="4" max="4" width="40.5546875" customWidth="1"/>
     <col min="5" max="5" width="39.109375" customWidth="1"/>
-    <col min="7" max="7" width="14.33203125" customWidth="1"/>
-    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="6" max="6" width="18.21875" customWidth="1"/>
+    <col min="7" max="7" width="32.44140625" customWidth="1"/>
+    <col min="8" max="8" width="47.44140625" customWidth="1"/>
     <col min="9" max="10" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -886,8 +1333,14 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G1" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -900,8 +1353,20 @@
       <c r="D2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E2" t="s">
+        <v>237</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -914,8 +1379,20 @@
       <c r="D3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E3" t="s">
+        <v>238</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>13</v>
       </c>
@@ -928,8 +1405,20 @@
       <c r="D4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E4" t="s">
+        <v>239</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>16</v>
       </c>
@@ -942,8 +1431,20 @@
       <c r="D5" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E5" t="s">
+        <v>240</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>19</v>
       </c>
@@ -956,8 +1457,20 @@
       <c r="D6" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>22</v>
       </c>
@@ -970,8 +1483,20 @@
       <c r="D7" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E7" t="s">
+        <v>241</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>26</v>
       </c>
@@ -984,8 +1509,20 @@
       <c r="D8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E8" t="s">
+        <v>242</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>29</v>
       </c>
@@ -998,8 +1535,20 @@
       <c r="D9" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E9" t="s">
+        <v>243</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>32</v>
       </c>
@@ -1012,8 +1561,20 @@
       <c r="D10" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E10" t="s">
+        <v>244</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>35</v>
       </c>
@@ -1026,8 +1587,20 @@
       <c r="D11" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E11" t="s">
+        <v>245</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>38</v>
       </c>
@@ -1040,8 +1613,20 @@
       <c r="D12" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E12" t="s">
+        <v>246</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>41</v>
       </c>
@@ -1054,8 +1639,20 @@
       <c r="D13" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E13" t="s">
+        <v>247</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>44</v>
       </c>
@@ -1068,8 +1665,20 @@
       <c r="D14" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E14" t="s">
+        <v>248</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>47</v>
       </c>
@@ -1082,8 +1691,20 @@
       <c r="D15" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E15" t="s">
+        <v>249</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>50</v>
       </c>
@@ -1096,8 +1717,20 @@
       <c r="D16" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E16" t="s">
+        <v>250</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>53</v>
       </c>
@@ -1110,8 +1743,20 @@
       <c r="D17" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E17" t="s">
+        <v>251</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>56</v>
       </c>
@@ -1124,8 +1769,20 @@
       <c r="D18" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E18" t="s">
+        <v>252</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>59</v>
       </c>
@@ -1138,8 +1795,20 @@
       <c r="D19" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E19" t="s">
+        <v>253</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>62</v>
       </c>
@@ -1152,8 +1821,20 @@
       <c r="D20" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E20" t="s">
+        <v>254</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>65</v>
       </c>
@@ -1166,8 +1847,20 @@
       <c r="D21" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E21" t="s">
+        <v>255</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>68</v>
       </c>
@@ -1180,8 +1873,20 @@
       <c r="D22" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E22" t="s">
+        <v>256</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>71</v>
       </c>
@@ -1194,8 +1899,20 @@
       <c r="D23" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E23" t="s">
+        <v>257</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>74</v>
       </c>
@@ -1208,8 +1925,20 @@
       <c r="D24" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E24" t="s">
+        <v>258</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G24" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>77</v>
       </c>
@@ -1222,8 +1951,20 @@
       <c r="D25" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E25" t="s">
+        <v>79</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>80</v>
       </c>
@@ -1236,8 +1977,20 @@
       <c r="D26" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E26" t="s">
+        <v>82</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G26" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>83</v>
       </c>
@@ -1250,8 +2003,20 @@
       <c r="D27" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E27" t="s">
+        <v>259</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
         <v>86</v>
       </c>
@@ -1264,8 +2029,20 @@
       <c r="D28" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E28" t="s">
+        <v>260</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G28" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>89</v>
       </c>
@@ -1278,8 +2055,20 @@
       <c r="D29" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E29" t="s">
+        <v>261</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>92</v>
       </c>
@@ -1292,8 +2081,20 @@
       <c r="D30" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E30" t="s">
+        <v>262</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G30" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>95</v>
       </c>
@@ -1306,8 +2107,20 @@
       <c r="D31" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E31" t="s">
+        <v>97</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>98</v>
       </c>
@@ -1320,8 +2133,20 @@
       <c r="D32" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E32" t="s">
+        <v>263</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G32" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>101</v>
       </c>
@@ -1334,8 +2159,20 @@
       <c r="D33" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E33" t="s">
+        <v>264</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="H33" s="7" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>104</v>
       </c>
@@ -1348,8 +2185,20 @@
       <c r="D34" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E34" t="s">
+        <v>106</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G34" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
         <v>107</v>
       </c>
@@ -1362,8 +2211,20 @@
       <c r="D35" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E35" t="s">
+        <v>265</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G35" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
         <v>110</v>
       </c>
@@ -1376,8 +2237,20 @@
       <c r="D36" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E36" t="s">
+        <v>266</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G36" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
         <v>113</v>
       </c>
@@ -1390,8 +2263,20 @@
       <c r="D37" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E37" t="s">
+        <v>115</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G37" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="H37" s="7" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
         <v>116</v>
       </c>
@@ -1404,8 +2289,20 @@
       <c r="D38" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E38" t="s">
+        <v>118</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G38" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
         <v>119</v>
       </c>
@@ -1418,8 +2315,20 @@
       <c r="D39" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E39" t="s">
+        <v>267</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G39" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="H39" s="7" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
         <v>122</v>
       </c>
@@ -1432,8 +2341,20 @@
       <c r="D40" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E40" t="s">
+        <v>268</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G40" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
         <v>125</v>
       </c>
@@ -1446,8 +2367,20 @@
       <c r="D41" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E41" t="s">
+        <v>269</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G41" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="H41" s="7" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
         <v>128</v>
       </c>
@@ -1460,8 +2393,20 @@
       <c r="D42" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E42" t="s">
+        <v>270</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G42" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
         <v>131</v>
       </c>
@@ -1474,8 +2419,20 @@
       <c r="D43" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E43" t="s">
+        <v>271</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G43" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="H43" s="7" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
         <v>134</v>
       </c>
@@ -1488,8 +2445,20 @@
       <c r="D44" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E44" t="s">
+        <v>272</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G44" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="H44" s="6" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
         <v>137</v>
       </c>
@@ -1502,8 +2471,20 @@
       <c r="D45" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E45" t="s">
+        <v>273</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G45" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="H45" s="7" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
         <v>140</v>
       </c>
@@ -1516,8 +2497,20 @@
       <c r="D46" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E46" s="11" t="s">
+        <v>279</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G46" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
         <v>143</v>
       </c>
@@ -1530,8 +2523,20 @@
       <c r="D47" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E47" t="s">
+        <v>274</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G47" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="H47" s="7" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
         <v>146</v>
       </c>
@@ -1544,8 +2549,20 @@
       <c r="D48" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E48" t="s">
+        <v>275</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G48" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="H48" s="6" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
         <v>149</v>
       </c>
@@ -1558,8 +2575,20 @@
       <c r="D49" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E49" t="s">
+        <v>276</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G49" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="H49" s="7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
         <v>152</v>
       </c>
@@ -1572,8 +2601,20 @@
       <c r="D50" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E50" t="s">
+        <v>277</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G50" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="H50" s="6" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
         <v>155</v>
       </c>
@@ -1586,8 +2627,23 @@
       <c r="D51" t="s">
         <v>157</v>
       </c>
+      <c r="E51" t="s">
+        <v>278</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G51" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="H51" s="7" t="s">
+        <v>235</v>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E46" r:id="rId1" display="http://www.google.com/" xr:uid="{A477FEC8-2C03-4AB8-8832-5E73A3CF6440}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>